--- a/config/auto_configs/2025_Hyundai_Kia_Niro(SG2 PHEV)_G 1.6 GDI KAPPA PE.xlsx
+++ b/config/auto_configs/2025_Hyundai_Kia_Niro(SG2 PHEV)_G 1.6 GDI KAPPA PE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,7 +525,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KMA_10050</t>
+          <t>KMA_HK_00734</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KMA_HK_00734</t>
+          <t>KMA_10050</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,6 +578,182 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KMA_HK_00731</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KMA_HK_00732</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KMA_HK_00736</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KMA_HK_00737</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KMA_HK_00738</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KMA_HK_00739</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>APSU</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KMA_HK_00740</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KMA_HK_00741</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>00</t>
         </is>
